--- a/testData/Opencart_LoginData.xlsx
+++ b/testData/Opencart_LoginData.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{28A1E83C-2B11-4F67-A932-F21AEE76A317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2448" windowWidth="8556" windowHeight="4656"/>
+    <workbookView xWindow="1152" yWindow="960" windowWidth="8772" windowHeight="8160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet" sheetId="1" r:id="rId1"/>
@@ -17,21 +18,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="47">
   <si>
     <t>username</t>
   </si>
@@ -166,12 +161,18 @@
   </si>
   <si>
     <t>4MuIrUIdnf7OYgO</t>
+  </si>
+  <si>
+    <t>kent_test@gmail.com</t>
+  </si>
+  <si>
+    <t>testp@$$w0rd123</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -246,7 +247,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -258,6 +259,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -567,15 +571,15 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.88671875" bestFit="1" customWidth="1"/>
@@ -583,7 +587,7 @@
     <col min="3" max="3" width="9.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" customFormat="1" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -594,20 +598,20 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:3" customFormat="1" ht="21" x14ac:dyDescent="0.4">
+      <c r="A2" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" customFormat="1" ht="21" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A3" s="2" t="s">
-        <v>7</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>6</v>
@@ -616,154 +620,167 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="21" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" customFormat="1" ht="21" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" customFormat="1" ht="21" x14ac:dyDescent="0.4">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
+      <c r="B5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" customFormat="1" ht="21" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
         <v>33</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A6" s="4" t="s">
+      <c r="C6" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" customFormat="1" ht="21" x14ac:dyDescent="0.4">
+      <c r="A7" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A7" s="4" t="s">
+      <c r="C7" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" customFormat="1" ht="21" x14ac:dyDescent="0.4">
+      <c r="A8" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A8" s="4" t="s">
+      <c r="C8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" customFormat="1" ht="21" x14ac:dyDescent="0.4">
+      <c r="A9" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A9" s="4" t="s">
+      <c r="C9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" customFormat="1" ht="21" x14ac:dyDescent="0.4">
+      <c r="A10" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A10" s="4" t="s">
+      <c r="C10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" customFormat="1" ht="21" x14ac:dyDescent="0.4">
+      <c r="A11" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A11" s="4" t="s">
+      <c r="C11" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" customFormat="1" ht="21" x14ac:dyDescent="0.4">
+      <c r="A12" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A12" s="4" t="s">
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" customFormat="1" ht="21" x14ac:dyDescent="0.4">
+      <c r="A13" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A13" s="4" t="s">
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" customFormat="1" ht="21" x14ac:dyDescent="0.4">
+      <c r="A14" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A14" s="4" t="s">
+      <c r="B14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" customFormat="1" ht="21" x14ac:dyDescent="0.4">
+      <c r="A15" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A15" s="4" t="s">
+      <c r="B15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" customFormat="1" ht="21" x14ac:dyDescent="0.4">
+      <c r="A16" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="3" t="s">
+      <c r="B16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>4</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A3" r:id="rId1" display="lakshmi@yahoo.com"/>
-    <hyperlink ref="A12" r:id="rId2"/>
-    <hyperlink ref="A13" r:id="rId3"/>
-    <hyperlink ref="A14" r:id="rId4"/>
-    <hyperlink ref="A15" r:id="rId5"/>
-    <hyperlink ref="A11" r:id="rId6"/>
+    <hyperlink ref="A4" r:id="rId1" display="lakshmi@yahoo.com" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="A13" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="A14" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="A15" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="A16" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="A12" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="A2" r:id="rId7" xr:uid="{9B16169B-489B-4144-8DE7-1ACCAF54C263}"/>
+    <hyperlink ref="B2" r:id="rId8" xr:uid="{5BBE46D1-D998-44A8-A914-026D1134B936}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId7"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -928,25 +945,25 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A3" r:id="rId1" display="lakshmi@yahoo.com"/>
-    <hyperlink ref="A5" r:id="rId2"/>
-    <hyperlink ref="A6" r:id="rId3"/>
-    <hyperlink ref="A7" r:id="rId4"/>
-    <hyperlink ref="A8:A14" r:id="rId5" display="kent.test3@gmail.com"/>
-    <hyperlink ref="A8" r:id="rId6"/>
-    <hyperlink ref="A9" r:id="rId7"/>
-    <hyperlink ref="A10" r:id="rId8"/>
-    <hyperlink ref="A11" r:id="rId9"/>
-    <hyperlink ref="A12" r:id="rId10"/>
-    <hyperlink ref="A13" r:id="rId11"/>
-    <hyperlink ref="A14" r:id="rId12"/>
+    <hyperlink ref="A3" r:id="rId1" display="lakshmi@yahoo.com" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="A5" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="A6" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
+    <hyperlink ref="A7" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
+    <hyperlink ref="A8:A14" r:id="rId5" display="kent.test3@gmail.com" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
+    <hyperlink ref="A8" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
+    <hyperlink ref="A9" r:id="rId7" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
+    <hyperlink ref="A10" r:id="rId8" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
+    <hyperlink ref="A11" r:id="rId9" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
+    <hyperlink ref="A12" r:id="rId10" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
+    <hyperlink ref="A13" r:id="rId11" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
+    <hyperlink ref="A14" r:id="rId12" xr:uid="{00000000-0004-0000-0100-00000B000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -1095,20 +1112,20 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1"/>
-    <hyperlink ref="A4" r:id="rId2"/>
-    <hyperlink ref="A5" r:id="rId3"/>
-    <hyperlink ref="A6" r:id="rId4"/>
-    <hyperlink ref="A7:A13" r:id="rId5" display="kent.test3@gmail.com"/>
-    <hyperlink ref="A7" r:id="rId6"/>
-    <hyperlink ref="A8" r:id="rId7"/>
-    <hyperlink ref="A9" r:id="rId8"/>
-    <hyperlink ref="A10" r:id="rId9"/>
-    <hyperlink ref="A11" r:id="rId10"/>
-    <hyperlink ref="A12" r:id="rId11"/>
-    <hyperlink ref="A13" r:id="rId12"/>
-    <hyperlink ref="A1" r:id="rId13"/>
-    <hyperlink ref="A3" r:id="rId14"/>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
+    <hyperlink ref="A4" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
+    <hyperlink ref="A5" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
+    <hyperlink ref="A6" r:id="rId4" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
+    <hyperlink ref="A7:A13" r:id="rId5" display="kent.test3@gmail.com" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
+    <hyperlink ref="A7" r:id="rId6" xr:uid="{00000000-0004-0000-0200-000005000000}"/>
+    <hyperlink ref="A8" r:id="rId7" xr:uid="{00000000-0004-0000-0200-000006000000}"/>
+    <hyperlink ref="A9" r:id="rId8" xr:uid="{00000000-0004-0000-0200-000007000000}"/>
+    <hyperlink ref="A10" r:id="rId9" xr:uid="{00000000-0004-0000-0200-000008000000}"/>
+    <hyperlink ref="A11" r:id="rId10" xr:uid="{00000000-0004-0000-0200-000009000000}"/>
+    <hyperlink ref="A12" r:id="rId11" xr:uid="{00000000-0004-0000-0200-00000A000000}"/>
+    <hyperlink ref="A13" r:id="rId12" xr:uid="{00000000-0004-0000-0200-00000B000000}"/>
+    <hyperlink ref="A1" r:id="rId13" xr:uid="{00000000-0004-0000-0200-00000C000000}"/>
+    <hyperlink ref="A3" r:id="rId14" xr:uid="{00000000-0004-0000-0200-00000D000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
